--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/MPI_2026_T1_Chaco_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/MPI_2026_T1_Chaco_CON_ERRORES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/MPI_2026_T1_Chaco_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/MPI_2026_T1_Chaco_CON_ERRORES.xlsx
@@ -1486,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="BJ4" s="6" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>45822</v>
+        <v>45823</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="BJ5" s="6" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="BJ6" s="6" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="BJ7" s="6" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="BJ8" s="6" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="BJ9" s="6" t="n">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="BJ10" s="6" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>45765</v>
+        <v>45766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="BJ11" s="6" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="BJ12" s="6" t="n">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="BJ13" s="6" t="n">
-        <v>45787</v>
+        <v>45788</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="BJ14" s="6" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="BJ15" s="6" t="n">
-        <v>45942</v>
+        <v>45943</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="BJ16" s="6" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="BJ17" s="6" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="BJ18" s="6" t="n">
-        <v>45598</v>
+        <v>45599</v>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>45805</v>
+        <v>45806</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="BJ19" s="6" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="BJ20" s="6" t="n">
-        <v>45779</v>
+        <v>45780</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="BJ21" s="6" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>45895</v>
+        <v>45896</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="BJ22" s="6" t="n">
-        <v>45643</v>
+        <v>45644</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45835</v>
+        <v>45836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="BJ23" s="6" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="BJ24" s="6" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="BJ25" s="6" t="n">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         </is>
       </c>
       <c r="BJ26" s="6" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="BJ27" s="6" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="BJ28" s="6" t="n">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="BJ29" s="6" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="BJ30" s="6" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="BJ31" s="6" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         </is>
       </c>
       <c r="BJ32" s="6" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="BJ33" s="6" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="BJ34" s="6" t="n">
-        <v>45591</v>
+        <v>45592</v>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="BJ35" s="6" t="n">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="BK35" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>999</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         </is>
       </c>
       <c r="BJ36" s="6" t="n">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="BK36" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
     <row r="38">
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="6" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="BJ38" s="6" t="n">
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>999</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         </is>
       </c>
       <c r="BJ39" s="6" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="BK39" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>999</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         </is>
       </c>
       <c r="BJ40" s="6" t="n">
-        <v>45866</v>
+        <v>45867</v>
       </c>
       <c r="BK40" t="inlineStr">
         <is>
